--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478926</v>
+        <v>122478999</v>
       </c>
       <c r="B2" t="n">
-        <v>105308</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591005</v>
+        <v>591025</v>
       </c>
       <c r="R2" t="n">
-        <v>6440773</v>
+        <v>6440712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478938</v>
+        <v>122478910</v>
       </c>
       <c r="B3" t="n">
-        <v>90828</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590999</v>
+        <v>590989</v>
       </c>
       <c r="R3" t="n">
-        <v>6440778</v>
+        <v>6440774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478859</v>
+        <v>122478970</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>105308</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +909,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590978</v>
+        <v>591023</v>
       </c>
       <c r="R4" t="n">
-        <v>6440698</v>
+        <v>6440743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,6 +989,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478878</v>
+        <v>122478938</v>
       </c>
       <c r="B5" t="n">
-        <v>98202</v>
+        <v>90828</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,35 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590966</v>
+        <v>590999</v>
       </c>
       <c r="R5" t="n">
-        <v>6440757</v>
+        <v>6440778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478896</v>
+        <v>122478981</v>
       </c>
       <c r="B6" t="n">
-        <v>90808</v>
+        <v>98202</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,38 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1172,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590974</v>
+        <v>591023</v>
       </c>
       <c r="R6" t="n">
-        <v>6440780</v>
+        <v>6440737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478885</v>
+        <v>122478859</v>
       </c>
       <c r="B7" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,35 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590969</v>
+        <v>590978</v>
       </c>
       <c r="R7" t="n">
-        <v>6440772</v>
+        <v>6440698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,7 +1325,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1346,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478999</v>
+        <v>122478878</v>
       </c>
       <c r="B8" t="n">
         <v>98202</v>
@@ -1394,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591025</v>
+        <v>590966</v>
       </c>
       <c r="R8" t="n">
-        <v>6440712</v>
+        <v>6440757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478950</v>
+        <v>122478885</v>
       </c>
       <c r="B9" t="n">
-        <v>91211</v>
+        <v>98202</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,38 +1466,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591009</v>
+        <v>590969</v>
       </c>
       <c r="R9" t="n">
-        <v>6440792</v>
+        <v>6440772</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478910</v>
+        <v>122478950</v>
       </c>
       <c r="B10" t="n">
-        <v>98202</v>
+        <v>91211</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1577,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590989</v>
+        <v>591009</v>
       </c>
       <c r="R10" t="n">
-        <v>6440774</v>
+        <v>6440792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,7 +1679,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478970</v>
+        <v>122478926</v>
       </c>
       <c r="B11" t="n">
         <v>105308</v>
@@ -1730,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591023</v>
+        <v>591005</v>
       </c>
       <c r="R11" t="n">
-        <v>6440743</v>
+        <v>6440773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478981</v>
+        <v>122478896</v>
       </c>
       <c r="B12" t="n">
-        <v>98202</v>
+        <v>90808</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,35 +1802,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591023</v>
+        <v>590974</v>
       </c>
       <c r="R12" t="n">
-        <v>6440737</v>
+        <v>6440780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478999</v>
+        <v>122478926</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>105317</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591025</v>
+        <v>591005</v>
       </c>
       <c r="R2" t="n">
-        <v>6440712</v>
+        <v>6440773</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478910</v>
+        <v>122478938</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>90833</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +793,33 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590989</v>
+        <v>590999</v>
       </c>
       <c r="R3" t="n">
-        <v>6440774</v>
+        <v>6440778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478970</v>
+        <v>122478999</v>
       </c>
       <c r="B4" t="n">
-        <v>105308</v>
+        <v>98211</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +902,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +933,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591023</v>
+        <v>591025</v>
       </c>
       <c r="R4" t="n">
-        <v>6440743</v>
+        <v>6440712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478938</v>
+        <v>122478981</v>
       </c>
       <c r="B5" t="n">
-        <v>90828</v>
+        <v>98211</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1008,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590999</v>
+        <v>591023</v>
       </c>
       <c r="R5" t="n">
-        <v>6440778</v>
+        <v>6440737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478981</v>
+        <v>122478896</v>
       </c>
       <c r="B6" t="n">
-        <v>98202</v>
+        <v>90813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1114,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591023</v>
+        <v>590974</v>
       </c>
       <c r="R6" t="n">
-        <v>6440737</v>
+        <v>6440780</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1211,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478859</v>
+        <v>122478950</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>91216</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1223,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>5420</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1257,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590978</v>
+        <v>591009</v>
       </c>
       <c r="R7" t="n">
-        <v>6440698</v>
+        <v>6440792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,6 +1301,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1320,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478878</v>
+        <v>122478910</v>
       </c>
       <c r="B8" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,11 +1337,6 @@
       </c>
       <c r="E8" t="n">
         <v>220787</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1391,10 +1363,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590966</v>
+        <v>590989</v>
       </c>
       <c r="R8" t="n">
-        <v>6440757</v>
+        <v>6440774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1426,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478885</v>
+        <v>122478859</v>
       </c>
       <c r="B9" t="n">
-        <v>98202</v>
+        <v>57395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,35 +1438,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1469,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590969</v>
+        <v>590978</v>
       </c>
       <c r="R9" t="n">
-        <v>6440772</v>
+        <v>6440698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1513,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478950</v>
+        <v>122478970</v>
       </c>
       <c r="B10" t="n">
-        <v>91211</v>
+        <v>105317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,34 +1547,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591009</v>
+        <v>591023</v>
       </c>
       <c r="R10" t="n">
-        <v>6440792</v>
+        <v>6440743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1637,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478926</v>
+        <v>122478878</v>
       </c>
       <c r="B11" t="n">
-        <v>105308</v>
+        <v>98211</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,25 +1649,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591005</v>
+        <v>590966</v>
       </c>
       <c r="R11" t="n">
-        <v>6440773</v>
+        <v>6440757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1743,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478896</v>
+        <v>122478885</v>
       </c>
       <c r="B12" t="n">
-        <v>90808</v>
+        <v>98211</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,38 +1755,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>220787</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1786,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590974</v>
+        <v>590969</v>
       </c>
       <c r="R12" t="n">
-        <v>6440780</v>
+        <v>6440772</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478926</v>
+        <v>122478970</v>
       </c>
       <c r="B2" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -718,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591005</v>
+        <v>591023</v>
       </c>
       <c r="R2" t="n">
-        <v>6440773</v>
+        <v>6440743</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478938</v>
+        <v>122478950</v>
       </c>
       <c r="B3" t="n">
-        <v>90833</v>
+        <v>91229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,20 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590999</v>
+        <v>591009</v>
       </c>
       <c r="R3" t="n">
-        <v>6440778</v>
+        <v>6440792</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478999</v>
+        <v>122478910</v>
       </c>
       <c r="B4" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,6 +917,11 @@
       </c>
       <c r="E4" t="n">
         <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -933,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591025</v>
+        <v>590989</v>
       </c>
       <c r="R4" t="n">
-        <v>6440712</v>
+        <v>6440774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478981</v>
+        <v>122478885</v>
       </c>
       <c r="B5" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,6 +1028,11 @@
       </c>
       <c r="E5" t="n">
         <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1039,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591023</v>
+        <v>590969</v>
       </c>
       <c r="R5" t="n">
-        <v>6440737</v>
+        <v>6440772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478896</v>
+        <v>122478878</v>
       </c>
       <c r="B6" t="n">
-        <v>90813</v>
+        <v>98224</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,33 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1148,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590974</v>
+        <v>590966</v>
       </c>
       <c r="R6" t="n">
-        <v>6440780</v>
+        <v>6440757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478950</v>
+        <v>122478896</v>
       </c>
       <c r="B7" t="n">
-        <v>91216</v>
+        <v>90826</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1223,20 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1246,7 +1273,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1257,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591009</v>
+        <v>590974</v>
       </c>
       <c r="R7" t="n">
-        <v>6440792</v>
+        <v>6440780</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478910</v>
+        <v>122478859</v>
       </c>
       <c r="B8" t="n">
-        <v>98211</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,30 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1363,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590989</v>
+        <v>590978</v>
       </c>
       <c r="R8" t="n">
-        <v>6440774</v>
+        <v>6440698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1439,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1426,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478859</v>
+        <v>122478938</v>
       </c>
       <c r="B9" t="n">
-        <v>57395</v>
+        <v>90846</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1442,26 +1473,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1469,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590978</v>
+        <v>590999</v>
       </c>
       <c r="R9" t="n">
-        <v>6440698</v>
+        <v>6440778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,6 +1552,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1531,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478970</v>
+        <v>122478926</v>
       </c>
       <c r="B10" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,6 +1588,11 @@
       </c>
       <c r="E10" t="n">
         <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1574,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591023</v>
+        <v>591005</v>
       </c>
       <c r="R10" t="n">
-        <v>6440743</v>
+        <v>6440773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478878</v>
+        <v>122478999</v>
       </c>
       <c r="B11" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1654,6 +1699,11 @@
       </c>
       <c r="E11" t="n">
         <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1680,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590966</v>
+        <v>591025</v>
       </c>
       <c r="R11" t="n">
-        <v>6440757</v>
+        <v>6440712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478885</v>
+        <v>122478981</v>
       </c>
       <c r="B12" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1760,6 +1810,11 @@
       </c>
       <c r="E12" t="n">
         <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1786,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590969</v>
+        <v>591023</v>
       </c>
       <c r="R12" t="n">
-        <v>6440772</v>
+        <v>6440737</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478970</v>
+        <v>122478885</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591023</v>
+        <v>590969</v>
       </c>
       <c r="R2" t="n">
-        <v>6440743</v>
+        <v>6440772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478950</v>
+        <v>122478970</v>
       </c>
       <c r="B3" t="n">
-        <v>91229</v>
+        <v>105343</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591009</v>
+        <v>591023</v>
       </c>
       <c r="R3" t="n">
-        <v>6440792</v>
+        <v>6440743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478910</v>
+        <v>122478926</v>
       </c>
       <c r="B4" t="n">
-        <v>98224</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +909,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590989</v>
+        <v>591005</v>
       </c>
       <c r="R4" t="n">
-        <v>6440774</v>
+        <v>6440773</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478885</v>
+        <v>122478938</v>
       </c>
       <c r="B5" t="n">
-        <v>98224</v>
+        <v>90859</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590969</v>
+        <v>590999</v>
       </c>
       <c r="R5" t="n">
-        <v>6440772</v>
+        <v>6440778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478878</v>
+        <v>122478896</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>90839</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590966</v>
+        <v>590974</v>
       </c>
       <c r="R6" t="n">
-        <v>6440757</v>
+        <v>6440780</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478896</v>
+        <v>122478910</v>
       </c>
       <c r="B7" t="n">
-        <v>90826</v>
+        <v>98237</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1248,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590974</v>
+        <v>590989</v>
       </c>
       <c r="R7" t="n">
-        <v>6440780</v>
+        <v>6440774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478859</v>
+        <v>122478999</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,35 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590978</v>
+        <v>591025</v>
       </c>
       <c r="R8" t="n">
-        <v>6440698</v>
+        <v>6440712</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,6 +1439,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1457,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478938</v>
+        <v>122478950</v>
       </c>
       <c r="B9" t="n">
-        <v>90846</v>
+        <v>91242</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,25 +1470,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1508,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590999</v>
+        <v>591009</v>
       </c>
       <c r="R9" t="n">
-        <v>6440778</v>
+        <v>6440792</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478926</v>
+        <v>122478859</v>
       </c>
       <c r="B10" t="n">
-        <v>105330</v>
+        <v>57399</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1584,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591005</v>
+        <v>590978</v>
       </c>
       <c r="R10" t="n">
-        <v>6440773</v>
+        <v>6440698</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1664,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1682,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478999</v>
+        <v>122478981</v>
       </c>
       <c r="B11" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591025</v>
+        <v>591023</v>
       </c>
       <c r="R11" t="n">
-        <v>6440712</v>
+        <v>6440737</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478981</v>
+        <v>122478878</v>
       </c>
       <c r="B12" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R12" t="n">
-        <v>6440737</v>
+        <v>6440757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478885</v>
+        <v>122478896</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590969</v>
+        <v>590974</v>
       </c>
       <c r="R2" t="n">
-        <v>6440772</v>
+        <v>6440780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478970</v>
+        <v>122478878</v>
       </c>
       <c r="B3" t="n">
-        <v>105343</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +801,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R3" t="n">
-        <v>6440743</v>
+        <v>6440757</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478926</v>
+        <v>122478950</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>91242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,31 +916,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -945,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591005</v>
+        <v>591009</v>
       </c>
       <c r="R4" t="n">
-        <v>6440773</v>
+        <v>6440792</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478938</v>
+        <v>122478859</v>
       </c>
       <c r="B5" t="n">
-        <v>90859</v>
+        <v>57399</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,34 +1030,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590999</v>
+        <v>590978</v>
       </c>
       <c r="R5" t="n">
-        <v>6440778</v>
+        <v>6440698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1106,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478896</v>
+        <v>122478981</v>
       </c>
       <c r="B6" t="n">
-        <v>90839</v>
+        <v>98237</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1136,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590974</v>
+        <v>591023</v>
       </c>
       <c r="R6" t="n">
-        <v>6440780</v>
+        <v>6440737</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,7 +1235,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478910</v>
+        <v>122478999</v>
       </c>
       <c r="B7" t="n">
         <v>98237</v>
@@ -1284,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590989</v>
+        <v>591025</v>
       </c>
       <c r="R7" t="n">
-        <v>6440774</v>
+        <v>6440712</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478999</v>
+        <v>122478970</v>
       </c>
       <c r="B8" t="n">
-        <v>98237</v>
+        <v>105343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1358,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591025</v>
+        <v>591023</v>
       </c>
       <c r="R8" t="n">
-        <v>6440712</v>
+        <v>6440743</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478950</v>
+        <v>122478926</v>
       </c>
       <c r="B9" t="n">
-        <v>91242</v>
+        <v>105343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1474,34 +1473,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591009</v>
+        <v>591005</v>
       </c>
       <c r="R9" t="n">
-        <v>6440792</v>
+        <v>6440773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478859</v>
+        <v>122478885</v>
       </c>
       <c r="B10" t="n">
-        <v>57399</v>
+        <v>98237</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1580,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590978</v>
+        <v>590969</v>
       </c>
       <c r="R10" t="n">
-        <v>6440698</v>
+        <v>6440772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,6 +1660,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1682,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478981</v>
+        <v>122478938</v>
       </c>
       <c r="B11" t="n">
-        <v>98237</v>
+        <v>90859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,35 +1691,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591023</v>
+        <v>590999</v>
       </c>
       <c r="R11" t="n">
-        <v>6440737</v>
+        <v>6440778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478878</v>
+        <v>122478910</v>
       </c>
       <c r="B12" t="n">
         <v>98237</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590966</v>
+        <v>590989</v>
       </c>
       <c r="R12" t="n">
-        <v>6440757</v>
+        <v>6440774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478896</v>
+        <v>122478950</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
+        <v>91243</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590974</v>
+        <v>591009</v>
       </c>
       <c r="R2" t="n">
-        <v>6440780</v>
+        <v>6440792</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478878</v>
+        <v>122478910</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590966</v>
+        <v>590989</v>
       </c>
       <c r="R3" t="n">
-        <v>6440757</v>
+        <v>6440774</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478950</v>
+        <v>122478970</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>105346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,34 +916,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591009</v>
+        <v>591023</v>
       </c>
       <c r="R4" t="n">
-        <v>6440792</v>
+        <v>6440743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478859</v>
+        <v>122478938</v>
       </c>
       <c r="B5" t="n">
-        <v>57399</v>
+        <v>90853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,31 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590978</v>
+        <v>590999</v>
       </c>
       <c r="R5" t="n">
-        <v>6440698</v>
+        <v>6440778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1124,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478981</v>
+        <v>122478878</v>
       </c>
       <c r="B6" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R6" t="n">
-        <v>6440737</v>
+        <v>6440757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478999</v>
+        <v>122478926</v>
       </c>
       <c r="B7" t="n">
-        <v>98237</v>
+        <v>105346</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1248,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591025</v>
+        <v>591005</v>
       </c>
       <c r="R7" t="n">
-        <v>6440712</v>
+        <v>6440773</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478970</v>
+        <v>122478885</v>
       </c>
       <c r="B8" t="n">
-        <v>105343</v>
+        <v>98240</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1394,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591023</v>
+        <v>590969</v>
       </c>
       <c r="R8" t="n">
-        <v>6440743</v>
+        <v>6440772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478926</v>
+        <v>122478896</v>
       </c>
       <c r="B9" t="n">
-        <v>105343</v>
+        <v>90833</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1469,35 +1470,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591005</v>
+        <v>590974</v>
       </c>
       <c r="R9" t="n">
-        <v>6440773</v>
+        <v>6440780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478885</v>
+        <v>122478999</v>
       </c>
       <c r="B10" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590969</v>
+        <v>591025</v>
       </c>
       <c r="R10" t="n">
-        <v>6440772</v>
+        <v>6440712</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478938</v>
+        <v>122478859</v>
       </c>
       <c r="B11" t="n">
-        <v>90859</v>
+        <v>57399</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,34 +1699,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590999</v>
+        <v>590978</v>
       </c>
       <c r="R11" t="n">
-        <v>6440778</v>
+        <v>6440698</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1775,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478910</v>
+        <v>122478981</v>
       </c>
       <c r="B12" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590989</v>
+        <v>591023</v>
       </c>
       <c r="R12" t="n">
-        <v>6440774</v>
+        <v>6440737</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478950</v>
+        <v>122478885</v>
       </c>
       <c r="B2" t="n">
-        <v>91243</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591009</v>
+        <v>590969</v>
       </c>
       <c r="R2" t="n">
-        <v>6440792</v>
+        <v>6440772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478910</v>
+        <v>122478999</v>
       </c>
       <c r="B3" t="n">
         <v>98240</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590989</v>
+        <v>591025</v>
       </c>
       <c r="R3" t="n">
-        <v>6440774</v>
+        <v>6440712</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478938</v>
+        <v>122478896</v>
       </c>
       <c r="B5" t="n">
-        <v>90853</v>
+        <v>90833</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1051,7 +1048,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1062,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590999</v>
+        <v>590974</v>
       </c>
       <c r="R5" t="n">
-        <v>6440778</v>
+        <v>6440780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478878</v>
+        <v>122478938</v>
       </c>
       <c r="B6" t="n">
-        <v>98240</v>
+        <v>90853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,35 +1134,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590966</v>
+        <v>590999</v>
       </c>
       <c r="R6" t="n">
-        <v>6440757</v>
+        <v>6440778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478926</v>
+        <v>122478950</v>
       </c>
       <c r="B7" t="n">
-        <v>105346</v>
+        <v>91243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1252,31 +1252,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1287,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591005</v>
+        <v>591009</v>
       </c>
       <c r="R7" t="n">
-        <v>6440773</v>
+        <v>6440792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1350,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478885</v>
+        <v>122478910</v>
       </c>
       <c r="B8" t="n">
         <v>98240</v>
@@ -1395,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590969</v>
+        <v>590989</v>
       </c>
       <c r="R8" t="n">
-        <v>6440772</v>
+        <v>6440774</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478896</v>
+        <v>122478981</v>
       </c>
       <c r="B9" t="n">
-        <v>90833</v>
+        <v>98240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,38 +1473,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590974</v>
+        <v>591023</v>
       </c>
       <c r="R9" t="n">
-        <v>6440780</v>
+        <v>6440737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478999</v>
+        <v>122478926</v>
       </c>
       <c r="B10" t="n">
-        <v>98240</v>
+        <v>105346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,25 +1584,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591025</v>
+        <v>591005</v>
       </c>
       <c r="R10" t="n">
-        <v>6440712</v>
+        <v>6440773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478981</v>
+        <v>122478878</v>
       </c>
       <c r="B12" t="n">
         <v>98240</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R12" t="n">
-        <v>6440737</v>
+        <v>6440757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478885</v>
+        <v>122478910</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590969</v>
+        <v>590989</v>
       </c>
       <c r="R2" t="n">
-        <v>6440772</v>
+        <v>6440774</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478999</v>
+        <v>122478859</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>57400</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591025</v>
+        <v>590978</v>
       </c>
       <c r="R3" t="n">
-        <v>6440712</v>
+        <v>6440698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -897,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478970</v>
+        <v>122478878</v>
       </c>
       <c r="B4" t="n">
-        <v>105346</v>
+        <v>98241</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R4" t="n">
-        <v>6440743</v>
+        <v>6440757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478896</v>
+        <v>122478950</v>
       </c>
       <c r="B5" t="n">
-        <v>90833</v>
+        <v>91244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,25 +1019,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1048,7 +1047,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1059,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590974</v>
+        <v>591009</v>
       </c>
       <c r="R5" t="n">
-        <v>6440780</v>
+        <v>6440792</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478938</v>
+        <v>122478970</v>
       </c>
       <c r="B6" t="n">
-        <v>90853</v>
+        <v>105347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1133,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590999</v>
+        <v>591023</v>
       </c>
       <c r="R6" t="n">
-        <v>6440778</v>
+        <v>6440743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478950</v>
+        <v>122478981</v>
       </c>
       <c r="B7" t="n">
-        <v>91243</v>
+        <v>98241</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,38 +1244,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591009</v>
+        <v>591023</v>
       </c>
       <c r="R7" t="n">
-        <v>6440792</v>
+        <v>6440737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478910</v>
+        <v>122478885</v>
       </c>
       <c r="B8" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590989</v>
+        <v>590969</v>
       </c>
       <c r="R8" t="n">
-        <v>6440774</v>
+        <v>6440772</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478981</v>
+        <v>122478896</v>
       </c>
       <c r="B9" t="n">
-        <v>98240</v>
+        <v>90834</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,35 +1466,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591023</v>
+        <v>590974</v>
       </c>
       <c r="R9" t="n">
-        <v>6440737</v>
+        <v>6440780</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478926</v>
+        <v>122478938</v>
       </c>
       <c r="B10" t="n">
-        <v>105346</v>
+        <v>90854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1580,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591005</v>
+        <v>590999</v>
       </c>
       <c r="R10" t="n">
-        <v>6440773</v>
+        <v>6440778</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1682,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478859</v>
+        <v>122478999</v>
       </c>
       <c r="B11" t="n">
-        <v>57399</v>
+        <v>98241</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,35 +1694,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590978</v>
+        <v>591025</v>
       </c>
       <c r="R11" t="n">
-        <v>6440698</v>
+        <v>6440712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,6 +1774,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478878</v>
+        <v>122478926</v>
       </c>
       <c r="B12" t="n">
-        <v>98240</v>
+        <v>105347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,25 +1805,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590966</v>
+        <v>591005</v>
       </c>
       <c r="R12" t="n">
-        <v>6440757</v>
+        <v>6440773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478910</v>
+        <v>122478938</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>90857</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590989</v>
+        <v>590999</v>
       </c>
       <c r="R2" t="n">
-        <v>6440774</v>
+        <v>6440778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478859</v>
+        <v>122478970</v>
       </c>
       <c r="B3" t="n">
-        <v>57400</v>
+        <v>105350</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590978</v>
+        <v>591023</v>
       </c>
       <c r="R3" t="n">
-        <v>6440698</v>
+        <v>6440743</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478878</v>
+        <v>122478981</v>
       </c>
       <c r="B4" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590966</v>
+        <v>591023</v>
       </c>
       <c r="R4" t="n">
-        <v>6440757</v>
+        <v>6440737</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478950</v>
+        <v>122478859</v>
       </c>
       <c r="B5" t="n">
-        <v>91244</v>
+        <v>57400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,38 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1058,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591009</v>
+        <v>590978</v>
       </c>
       <c r="R5" t="n">
-        <v>6440792</v>
+        <v>6440698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1102,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478970</v>
+        <v>122478878</v>
       </c>
       <c r="B6" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1133,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591023</v>
+        <v>590966</v>
       </c>
       <c r="R6" t="n">
-        <v>6440743</v>
+        <v>6440757</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478981</v>
+        <v>122478950</v>
       </c>
       <c r="B7" t="n">
-        <v>98241</v>
+        <v>91247</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,35 +1244,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1280,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591023</v>
+        <v>591009</v>
       </c>
       <c r="R7" t="n">
-        <v>6440737</v>
+        <v>6440792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478885</v>
+        <v>122478896</v>
       </c>
       <c r="B8" t="n">
-        <v>98241</v>
+        <v>90837</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1358,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590969</v>
+        <v>590974</v>
       </c>
       <c r="R8" t="n">
-        <v>6440772</v>
+        <v>6440780</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1460,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478896</v>
+        <v>122478926</v>
       </c>
       <c r="B9" t="n">
-        <v>90834</v>
+        <v>105350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,38 +1472,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1508,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590974</v>
+        <v>591005</v>
       </c>
       <c r="R9" t="n">
-        <v>6440780</v>
+        <v>6440773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478938</v>
+        <v>122478885</v>
       </c>
       <c r="B10" t="n">
-        <v>90854</v>
+        <v>98244</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1580,38 +1583,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1619,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590999</v>
+        <v>590969</v>
       </c>
       <c r="R10" t="n">
-        <v>6440778</v>
+        <v>6440772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1685,7 @@
         <v>122478999</v>
       </c>
       <c r="B11" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478926</v>
+        <v>122478910</v>
       </c>
       <c r="B12" t="n">
-        <v>105347</v>
+        <v>98244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,25 +1805,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591005</v>
+        <v>590989</v>
       </c>
       <c r="R12" t="n">
-        <v>6440773</v>
+        <v>6440774</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478938</v>
+        <v>122478878</v>
       </c>
       <c r="B2" t="n">
-        <v>90857</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590999</v>
+        <v>590966</v>
       </c>
       <c r="R2" t="n">
-        <v>6440778</v>
+        <v>6440757</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -900,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478981</v>
+        <v>122478938</v>
       </c>
       <c r="B4" t="n">
-        <v>98244</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591023</v>
+        <v>590999</v>
       </c>
       <c r="R4" t="n">
-        <v>6440737</v>
+        <v>6440778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478859</v>
+        <v>122478999</v>
       </c>
       <c r="B5" t="n">
-        <v>57400</v>
+        <v>98244</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590978</v>
+        <v>591025</v>
       </c>
       <c r="R5" t="n">
-        <v>6440698</v>
+        <v>6440712</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,6 +1103,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478878</v>
+        <v>122478910</v>
       </c>
       <c r="B6" t="n">
         <v>98244</v>
@@ -1169,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590966</v>
+        <v>590989</v>
       </c>
       <c r="R6" t="n">
-        <v>6440757</v>
+        <v>6440774</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478950</v>
+        <v>122478885</v>
       </c>
       <c r="B7" t="n">
-        <v>91247</v>
+        <v>98244</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1244,38 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1283,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591009</v>
+        <v>590969</v>
       </c>
       <c r="R7" t="n">
-        <v>6440792</v>
+        <v>6440772</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1346,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478896</v>
+        <v>122478981</v>
       </c>
       <c r="B8" t="n">
-        <v>90837</v>
+        <v>98244</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1358,38 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590974</v>
+        <v>591023</v>
       </c>
       <c r="R8" t="n">
-        <v>6440780</v>
+        <v>6440737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478926</v>
+        <v>122478859</v>
       </c>
       <c r="B9" t="n">
-        <v>105350</v>
+        <v>57400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1472,35 +1467,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1508,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591005</v>
+        <v>590978</v>
       </c>
       <c r="R9" t="n">
-        <v>6440773</v>
+        <v>6440698</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1547,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1571,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478885</v>
+        <v>122478950</v>
       </c>
       <c r="B10" t="n">
-        <v>98244</v>
+        <v>91247</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,35 +1577,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1619,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590969</v>
+        <v>591009</v>
       </c>
       <c r="R10" t="n">
-        <v>6440772</v>
+        <v>6440792</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478999</v>
+        <v>122478926</v>
       </c>
       <c r="B11" t="n">
-        <v>98244</v>
+        <v>105350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1694,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591025</v>
+        <v>591005</v>
       </c>
       <c r="R11" t="n">
-        <v>6440712</v>
+        <v>6440773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478910</v>
+        <v>122478896</v>
       </c>
       <c r="B12" t="n">
-        <v>98244</v>
+        <v>90837</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,35 +1802,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590989</v>
+        <v>590974</v>
       </c>
       <c r="R12" t="n">
-        <v>6440774</v>
+        <v>6440780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -1679,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478926</v>
+        <v>122478896</v>
       </c>
       <c r="B11" t="n">
-        <v>105350</v>
+        <v>90837</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,35 +1691,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1727,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591005</v>
+        <v>590974</v>
       </c>
       <c r="R11" t="n">
-        <v>6440773</v>
+        <v>6440780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478896</v>
+        <v>122478926</v>
       </c>
       <c r="B12" t="n">
-        <v>90837</v>
+        <v>105350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,38 +1805,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590974</v>
+        <v>591005</v>
       </c>
       <c r="R12" t="n">
-        <v>6440780</v>
+        <v>6440773</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -1679,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478896</v>
+        <v>122478926</v>
       </c>
       <c r="B11" t="n">
-        <v>90837</v>
+        <v>105350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,38 +1691,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1730,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590974</v>
+        <v>591005</v>
       </c>
       <c r="R11" t="n">
-        <v>6440780</v>
+        <v>6440773</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1793,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478926</v>
+        <v>122478896</v>
       </c>
       <c r="B12" t="n">
-        <v>105350</v>
+        <v>90837</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1805,35 +1802,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591005</v>
+        <v>590974</v>
       </c>
       <c r="R12" t="n">
-        <v>6440773</v>
+        <v>6440780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478878</v>
+        <v>122478926</v>
       </c>
       <c r="B2" t="n">
-        <v>98244</v>
+        <v>105453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590966</v>
+        <v>591005</v>
       </c>
       <c r="R2" t="n">
-        <v>6440757</v>
+        <v>6440773</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478970</v>
+        <v>122478938</v>
       </c>
       <c r="B3" t="n">
-        <v>105350</v>
+        <v>90960</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591023</v>
+        <v>590999</v>
       </c>
       <c r="R3" t="n">
-        <v>6440743</v>
+        <v>6440778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478938</v>
+        <v>122478970</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>105453</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590999</v>
+        <v>591023</v>
       </c>
       <c r="R4" t="n">
-        <v>6440778</v>
+        <v>6440743</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478999</v>
+        <v>122478885</v>
       </c>
       <c r="B5" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591025</v>
+        <v>590969</v>
       </c>
       <c r="R5" t="n">
-        <v>6440712</v>
+        <v>6440772</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478910</v>
+        <v>122478999</v>
       </c>
       <c r="B6" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590989</v>
+        <v>591025</v>
       </c>
       <c r="R6" t="n">
-        <v>6440774</v>
+        <v>6440712</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478885</v>
+        <v>122478859</v>
       </c>
       <c r="B7" t="n">
-        <v>98244</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590969</v>
+        <v>590978</v>
       </c>
       <c r="R7" t="n">
-        <v>6440772</v>
+        <v>6440698</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1325,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>122478981</v>
       </c>
       <c r="B8" t="n">
-        <v>98244</v>
+        <v>98347</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1455,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478859</v>
+        <v>122478910</v>
       </c>
       <c r="B9" t="n">
-        <v>57400</v>
+        <v>98347</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,35 +1466,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1503,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590978</v>
+        <v>590989</v>
       </c>
       <c r="R9" t="n">
-        <v>6440698</v>
+        <v>6440774</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1547,6 +1546,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1565,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478950</v>
+        <v>122478896</v>
       </c>
       <c r="B10" t="n">
-        <v>91247</v>
+        <v>90940</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,25 +1577,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591009</v>
+        <v>590974</v>
       </c>
       <c r="R10" t="n">
-        <v>6440792</v>
+        <v>6440780</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478926</v>
+        <v>122478878</v>
       </c>
       <c r="B11" t="n">
-        <v>105350</v>
+        <v>98347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591005</v>
+        <v>590966</v>
       </c>
       <c r="R11" t="n">
-        <v>6440773</v>
+        <v>6440757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478896</v>
+        <v>122478950</v>
       </c>
       <c r="B12" t="n">
-        <v>90837</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590974</v>
+        <v>591009</v>
       </c>
       <c r="R12" t="n">
-        <v>6440780</v>
+        <v>6440792</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478859</v>
+        <v>122478981</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>98347</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,35 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590978</v>
+        <v>591023</v>
       </c>
       <c r="R7" t="n">
-        <v>6440698</v>
+        <v>6440737</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478981</v>
+        <v>122478859</v>
       </c>
       <c r="B8" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591023</v>
+        <v>590978</v>
       </c>
       <c r="R8" t="n">
-        <v>6440737</v>
+        <v>6440698</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,7 +1436,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478926</v>
+        <v>122478938</v>
       </c>
       <c r="B2" t="n">
-        <v>105453</v>
+        <v>90964</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591005</v>
+        <v>590999</v>
       </c>
       <c r="R2" t="n">
-        <v>6440773</v>
+        <v>6440778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478938</v>
+        <v>122478878</v>
       </c>
       <c r="B3" t="n">
-        <v>90960</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590999</v>
+        <v>590966</v>
       </c>
       <c r="R3" t="n">
-        <v>6440778</v>
+        <v>6440757</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478970</v>
+        <v>122478999</v>
       </c>
       <c r="B4" t="n">
-        <v>105453</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,25 +912,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591023</v>
+        <v>591025</v>
       </c>
       <c r="R4" t="n">
-        <v>6440743</v>
+        <v>6440712</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478885</v>
+        <v>122478859</v>
       </c>
       <c r="B5" t="n">
-        <v>98347</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1023,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590969</v>
+        <v>590978</v>
       </c>
       <c r="R5" t="n">
-        <v>6440772</v>
+        <v>6440698</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1103,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478999</v>
+        <v>122478885</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1169,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591025</v>
+        <v>590969</v>
       </c>
       <c r="R6" t="n">
-        <v>6440712</v>
+        <v>6440772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478981</v>
+        <v>122478910</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591023</v>
+        <v>590989</v>
       </c>
       <c r="R7" t="n">
-        <v>6440737</v>
+        <v>6440774</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478859</v>
+        <v>122478981</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1355,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590978</v>
+        <v>591023</v>
       </c>
       <c r="R8" t="n">
-        <v>6440698</v>
+        <v>6440737</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,6 +1435,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478910</v>
+        <v>122478950</v>
       </c>
       <c r="B9" t="n">
-        <v>98347</v>
+        <v>91354</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,35 +1466,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1502,10 +1505,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590989</v>
+        <v>591009</v>
       </c>
       <c r="R9" t="n">
-        <v>6440774</v>
+        <v>6440792</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1565,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478896</v>
+        <v>122478926</v>
       </c>
       <c r="B10" t="n">
-        <v>90940</v>
+        <v>105461</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,38 +1580,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>590974</v>
+        <v>591005</v>
       </c>
       <c r="R10" t="n">
-        <v>6440780</v>
+        <v>6440773</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,10 +1679,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478878</v>
+        <v>122478970</v>
       </c>
       <c r="B11" t="n">
-        <v>98347</v>
+        <v>105461</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,25 +1691,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590966</v>
+        <v>591023</v>
       </c>
       <c r="R11" t="n">
-        <v>6440757</v>
+        <v>6440743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478950</v>
+        <v>122478896</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1802,25 +1802,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>591009</v>
+        <v>590974</v>
       </c>
       <c r="R12" t="n">
-        <v>6440792</v>
+        <v>6440780</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478938</v>
+        <v>122478885</v>
       </c>
       <c r="B2" t="n">
-        <v>90964</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590999</v>
+        <v>590969</v>
       </c>
       <c r="R2" t="n">
-        <v>6440778</v>
+        <v>6440772</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478878</v>
+        <v>122478896</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590966</v>
+        <v>590974</v>
       </c>
       <c r="R3" t="n">
-        <v>6440757</v>
+        <v>6440780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478999</v>
+        <v>122478878</v>
       </c>
       <c r="B4" t="n">
         <v>98355</v>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591025</v>
+        <v>590966</v>
       </c>
       <c r="R4" t="n">
-        <v>6440712</v>
+        <v>6440757</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478859</v>
+        <v>122478938</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,31 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590978</v>
+        <v>590999</v>
       </c>
       <c r="R5" t="n">
-        <v>6440698</v>
+        <v>6440778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,6 +1106,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1125,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478885</v>
+        <v>122478970</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>105461</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,25 +1137,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1169,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590969</v>
+        <v>591023</v>
       </c>
       <c r="R6" t="n">
-        <v>6440772</v>
+        <v>6440743</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1343,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478981</v>
+        <v>122478950</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1355,35 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1391,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591023</v>
+        <v>591009</v>
       </c>
       <c r="R8" t="n">
-        <v>6440737</v>
+        <v>6440792</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478950</v>
+        <v>122478981</v>
       </c>
       <c r="B9" t="n">
-        <v>91354</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1466,38 +1473,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1505,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591009</v>
+        <v>591023</v>
       </c>
       <c r="R9" t="n">
-        <v>6440792</v>
+        <v>6440737</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1679,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478970</v>
+        <v>122478999</v>
       </c>
       <c r="B11" t="n">
-        <v>105461</v>
+        <v>98355</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1691,25 +1695,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1727,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591023</v>
+        <v>591025</v>
       </c>
       <c r="R11" t="n">
-        <v>6440743</v>
+        <v>6440712</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478896</v>
+        <v>122478859</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>57494</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,34 +1810,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1841,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590974</v>
+        <v>590978</v>
       </c>
       <c r="R12" t="n">
-        <v>6440780</v>
+        <v>6440698</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1885,7 +1886,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4456-2025 artfynd.xlsx
+++ b/artfynd/A 4456-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122478885</v>
+        <v>122478999</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590969</v>
+        <v>591025</v>
       </c>
       <c r="R2" t="n">
-        <v>6440772</v>
+        <v>6440712</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122478896</v>
+        <v>122478859</v>
       </c>
       <c r="B3" t="n">
-        <v>90944</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,34 +802,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590974</v>
+        <v>590978</v>
       </c>
       <c r="R3" t="n">
-        <v>6440780</v>
+        <v>6440698</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +878,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122478878</v>
+        <v>122478910</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590966</v>
+        <v>590989</v>
       </c>
       <c r="R4" t="n">
-        <v>6440757</v>
+        <v>6440774</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122478938</v>
+        <v>122478981</v>
       </c>
       <c r="B5" t="n">
-        <v>90964</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1019,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1062,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590999</v>
+        <v>591023</v>
       </c>
       <c r="R5" t="n">
-        <v>6440778</v>
+        <v>6440737</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1125,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122478970</v>
+        <v>122478885</v>
       </c>
       <c r="B6" t="n">
-        <v>105461</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1137,25 +1130,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591023</v>
+        <v>590969</v>
       </c>
       <c r="R6" t="n">
-        <v>6440743</v>
+        <v>6440772</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122478910</v>
+        <v>122478950</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>91354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1241,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590989</v>
+        <v>591009</v>
       </c>
       <c r="R7" t="n">
-        <v>6440774</v>
+        <v>6440792</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122478950</v>
+        <v>122478878</v>
       </c>
       <c r="B8" t="n">
-        <v>91354</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1355,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>591009</v>
+        <v>590966</v>
       </c>
       <c r="R8" t="n">
-        <v>6440792</v>
+        <v>6440757</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122478981</v>
+        <v>122478926</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>105463</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,25 +1466,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>591023</v>
+        <v>591005</v>
       </c>
       <c r="R9" t="n">
-        <v>6440737</v>
+        <v>6440773</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1565,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122478926</v>
+        <v>122478970</v>
       </c>
       <c r="B10" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,10 +1613,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>591005</v>
+        <v>591023</v>
       </c>
       <c r="R10" t="n">
-        <v>6440773</v>
+        <v>6440743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1676,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122478999</v>
+        <v>122478896</v>
       </c>
       <c r="B11" t="n">
-        <v>98355</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,35 +1688,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1731,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>591025</v>
+        <v>590974</v>
       </c>
       <c r="R11" t="n">
-        <v>6440712</v>
+        <v>6440780</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122478859</v>
+        <v>122478938</v>
       </c>
       <c r="B12" t="n">
-        <v>57494</v>
+        <v>90964</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,31 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1842,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590978</v>
+        <v>590999</v>
       </c>
       <c r="R12" t="n">
-        <v>6440698</v>
+        <v>6440778</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,6 +1885,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
